--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260622.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260622.xlsx
@@ -821,17 +821,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>17,948,000</t>
+          <t>2,492,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -843,17 +843,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,492,000</t>
+          <t>17,948,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>4,833,848</t>
+          <t>5,058,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,058,000</t>
+          <t>4,833,848</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
